--- a/tables/B【表情表】Emoji.xlsx
+++ b/tables/B【表情表】Emoji.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" activeTab="1"/>
+    <workbookView windowHeight="17055"/>
   </bookViews>
   <sheets>
     <sheet name="@Type" sheetId="4" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="68">
   <si>
     <t>种类</t>
   </si>
@@ -102,25 +102,31 @@
     <t>Speed</t>
   </si>
   <si>
+    <t>float64</t>
+  </si>
+  <si>
+    <t>|</t>
+  </si>
+  <si>
+    <t>切图格子</t>
+  </si>
+  <si>
+    <t>Grids</t>
+  </si>
+  <si>
+    <t>ArrayDict</t>
+  </si>
+  <si>
+    <t>#id</t>
+  </si>
+  <si>
+    <t>#备注</t>
+  </si>
+  <si>
+    <t>#int</t>
+  </si>
+  <si>
     <t>float</t>
-  </si>
-  <si>
-    <t>切图格子</t>
-  </si>
-  <si>
-    <t>Grids</t>
-  </si>
-  <si>
-    <t>ArrayDict</t>
-  </si>
-  <si>
-    <t>#id</t>
-  </si>
-  <si>
-    <t>#备注</t>
-  </si>
-  <si>
-    <t>#int</t>
   </si>
   <si>
     <t>#note</t>
@@ -1335,7 +1341,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" s="15" customFormat="1" spans="1:5">
+    <row r="2" s="15" customFormat="1" spans="1:8">
       <c r="A2" s="15" t="s">
         <v>8</v>
       </c>
@@ -1352,7 +1358,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" s="15" customFormat="1" spans="1:5">
+    <row r="3" s="15" customFormat="1" spans="1:8">
       <c r="A3" s="15" t="s">
         <v>8</v>
       </c>
@@ -1369,7 +1375,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:8">
       <c r="A4" s="15" t="s">
         <v>8</v>
       </c>
@@ -1386,7 +1392,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:8">
       <c r="A5" s="15" t="s">
         <v>8</v>
       </c>
@@ -1403,7 +1409,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:8">
       <c r="A6" s="15" t="s">
         <v>8</v>
       </c>
@@ -1421,7 +1427,7 @@
       </c>
       <c r="F6" s="15"/>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:8">
       <c r="A7" s="15" t="s">
         <v>8</v>
       </c>
@@ -1437,9 +1443,11 @@
       <c r="E7" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="F7" s="15"/>
+      <c r="F7" s="15" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:8">
       <c r="A8" s="15" t="s">
         <v>8</v>
       </c>
@@ -1447,10 +1455,10 @@
         <v>9</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E8" s="15" t="s">
         <v>19</v>
@@ -1482,9 +1490,9 @@
     <col min="11" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:9">
+    <row r="1" s="1" customFormat="1" spans="1:10">
       <c r="A1" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>11</v>
@@ -1506,12 +1514,12 @@
         <v>23</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>10</v>
@@ -1533,15 +1541,15 @@
         <v>22</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:10">
       <c r="A3" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>12</v>
@@ -1560,7 +1568,7 @@
         <v>12</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="I3" s="5" t="s">
         <v>19</v>
@@ -1568,32 +1576,32 @@
     </row>
     <row r="4" s="2" customFormat="1" ht="25.5" spans="1:10">
       <c r="A4" s="7" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" s="3" customFormat="1" spans="1:10">
@@ -1601,22 +1609,22 @@
         <v>2</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F5" s="13">
         <v>0</v>
       </c>
       <c r="G5" s="13" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H5" s="9">
         <v>0.1</v>
@@ -1625,30 +1633,30 @@
         <v>9</v>
       </c>
       <c r="J5" s="9" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:10">
       <c r="A6" s="9">
         <v>8</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F6" s="1">
         <v>1</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H6" s="9">
         <v>0.1</v>
@@ -1657,27 +1665,27 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:10">
       <c r="A7" s="9">
         <v>10</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F7" s="1">
         <v>1</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H7" s="9">
         <v>0.1</v>
@@ -1686,27 +1694,27 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:10">
       <c r="A8" s="9">
         <v>12</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F8" s="1">
         <v>1</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H8" s="9">
         <v>0.1</v>
@@ -1715,27 +1723,27 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:10">
       <c r="A9" s="9">
         <v>14</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F9" s="1">
         <v>1</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H9" s="9">
         <v>0.1</v>
@@ -1744,27 +1752,27 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:10">
       <c r="A10" s="9">
         <v>15</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F10" s="1">
         <v>1</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H10" s="9">
         <v>0.1</v>
